--- a/hojas_de_datos/ResultadosDispatching.xlsx
+++ b/hojas_de_datos/ResultadosDispatching.xlsx
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>932700606092.6913</v>
+        <v>932700606092.6912</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
         <v>4254.3</v>
       </c>
       <c r="J17" t="n">
-        <v>20189.89653538321</v>
+        <v>17195.50853665947</v>
       </c>
       <c r="K17" t="n">
         <v>3312.1152</v>
@@ -2726,7 +2726,7 @@
         <v>-0</v>
       </c>
       <c r="C34" t="n">
-        <v>32546.22937177551</v>
+        <v>43169.55416563447</v>
       </c>
       <c r="D34" t="n">
         <v>-0</v>
@@ -5391,7 +5391,7 @@
         <v>-0</v>
       </c>
       <c r="C75" t="n">
-        <v>51523.78791062905</v>
+        <v>38203.03727766385</v>
       </c>
       <c r="D75" t="n">
         <v>-0</v>
@@ -5480,7 +5480,7 @@
         <v>-0</v>
       </c>
       <c r="K76" t="n">
-        <v>17099.80051157145</v>
+        <v>18734.1516</v>
       </c>
       <c r="L76" t="n">
         <v>-0</v>
@@ -5675,7 +5675,7 @@
         <v>-0</v>
       </c>
       <c r="K79" t="n">
-        <v>17047.51629566453</v>
+        <v>18975.66</v>
       </c>
       <c r="L79" t="n">
         <v>-0</v>
@@ -6127,7 +6127,7 @@
         <v>2542.8</v>
       </c>
       <c r="J86" t="n">
-        <v>25192.60192327091</v>
+        <v>24624.49512922839</v>
       </c>
       <c r="K86" t="n">
         <v>-0</v>
@@ -11046,7 +11046,7 @@
         <v>-0</v>
       </c>
       <c r="C162" t="n">
-        <v>54765.69094499559</v>
+        <v>57463.11678410183</v>
       </c>
       <c r="D162" t="n">
         <v>-0</v>
@@ -20979,7 +20979,7 @@
         <v>2876.476473888191</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1408.186641208351</v>
       </c>
     </row>
     <row r="91">
@@ -21035,7 +21035,7 @@
         <v>10000</v>
       </c>
       <c r="D94" t="n">
-        <v>1408.18664120835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -23362,7 +23362,7 @@
         <v>2876.476473888191</v>
       </c>
       <c r="D90" t="n">
-        <v>-0</v>
+        <v>1408.186641208351</v>
       </c>
     </row>
     <row r="91">
@@ -23418,7 +23418,7 @@
         <v>10000</v>
       </c>
       <c r="D94" t="n">
-        <v>1408.18664120835</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="95">
@@ -28128,7 +28128,7 @@
         <v>4992534.883626319</v>
       </c>
       <c r="D90" t="n">
-        <v>12000</v>
+        <v>10469.36234651266</v>
       </c>
     </row>
     <row r="91">
@@ -28142,7 +28142,7 @@
         <v>4982534.883626319</v>
       </c>
       <c r="D91" t="n">
-        <v>8739.130434782608</v>
+        <v>7208.492781295271</v>
       </c>
     </row>
     <row r="92">
@@ -28156,7 +28156,7 @@
         <v>4972534.883626319</v>
       </c>
       <c r="D92" t="n">
-        <v>5478.260869565217</v>
+        <v>3947.62321607788</v>
       </c>
     </row>
     <row r="93">
@@ -28170,7 +28170,7 @@
         <v>4962534.883626319</v>
       </c>
       <c r="D93" t="n">
-        <v>2217.391304347826</v>
+        <v>686.7536508604891</v>
       </c>
     </row>
     <row r="94">
@@ -29248,7 +29248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29524,6 +29524,24 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MA_hydrogen_bus</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29574,7 +29592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30065,6 +30083,35 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MA_hydrogen_bus</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="C16" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Slack</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -30079,7 +30126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30110,15 +30157,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>PT_water_bus</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>PT_hydrogen_bus</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PT_SRES_excedentes_bus</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>FR_hydrogen_bus</t>
         </is>
@@ -30152,6 +30204,9 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -30181,6 +30236,9 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -30210,6 +30268,9 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -30239,6 +30300,9 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -30268,6 +30332,9 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -30297,6 +30364,9 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -30326,6 +30396,9 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -30347,12 +30420,15 @@
         <v>-2.273736754432321e-13</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30384,6 +30460,9 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -30413,6 +30492,9 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -30434,12 +30516,15 @@
         <v>1.364242052659392e-12</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30463,12 +30548,15 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30500,6 +30588,9 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -30521,12 +30612,15 @@
         <v>1.818989403545856e-12</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30558,6 +30652,9 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -30576,7 +30673,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -30585,6 +30682,9 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30616,6 +30716,9 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -30645,6 +30748,9 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -30674,6 +30780,9 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -30703,6 +30812,9 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -30732,6 +30844,9 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -30761,6 +30876,9 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -30790,6 +30908,9 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -30819,6 +30940,9 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -30848,6 +30972,9 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -30877,6 +31004,9 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -30906,6 +31036,9 @@
       <c r="I28" t="n">
         <v>0</v>
       </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -30935,6 +31068,9 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -30964,6 +31100,9 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -30993,6 +31132,9 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -31014,12 +31156,15 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31051,6 +31196,9 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -31080,6 +31228,9 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -31109,6 +31260,9 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -31138,6 +31292,9 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -31167,6 +31324,9 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -31196,6 +31356,9 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -31225,6 +31388,9 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -31254,6 +31420,9 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -31283,6 +31452,9 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -31312,6 +31484,9 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -31341,6 +31516,9 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -31370,6 +31548,9 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -31399,6 +31580,9 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -31428,6 +31612,9 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -31457,6 +31644,9 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -31486,6 +31676,9 @@
       <c r="I48" t="n">
         <v>0</v>
       </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -31515,6 +31708,9 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -31544,6 +31740,9 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -31573,6 +31772,9 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -31602,6 +31804,9 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -31631,6 +31836,9 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -31660,6 +31868,9 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -31689,6 +31900,9 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -31718,6 +31932,9 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -31739,12 +31956,15 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
       <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31768,12 +31988,15 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>-4.547473508864641e-13</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31797,12 +32020,15 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
       <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31826,12 +32052,15 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
       <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31855,12 +32084,15 @@
         <v>-9.094947017729282e-13</v>
       </c>
       <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
       <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31884,12 +32116,15 @@
         <v>-9.094947017729282e-13</v>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31913,12 +32148,15 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
       <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31942,12 +32180,15 @@
         <v>-5.002220859751105e-12</v>
       </c>
       <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
       <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31971,12 +32212,15 @@
         <v>-9.094947017729282e-13</v>
       </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32000,12 +32244,15 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32029,12 +32276,15 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
       <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32058,12 +32308,15 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
       <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32095,6 +32348,9 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -32124,6 +32380,9 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -32153,6 +32412,9 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -32182,6 +32444,9 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -32211,6 +32476,9 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -32240,6 +32508,9 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -32269,6 +32540,9 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -32287,7 +32561,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -32296,6 +32570,9 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
         <v>-1.13686837721616e-13</v>
       </c>
     </row>
@@ -32327,6 +32604,9 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -32356,6 +32636,9 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -32374,7 +32657,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -32383,6 +32666,9 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32414,6 +32700,9 @@
       <c r="I80" t="n">
         <v>0</v>
       </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -32443,6 +32732,9 @@
       <c r="I81" t="n">
         <v>0</v>
       </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -32472,6 +32764,9 @@
       <c r="I82" t="n">
         <v>0</v>
       </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -32501,6 +32796,9 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -32530,6 +32828,9 @@
       <c r="I84" t="n">
         <v>0</v>
       </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -32559,6 +32860,9 @@
       <c r="I85" t="n">
         <v>0</v>
       </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -32588,6 +32892,9 @@
       <c r="I86" t="n">
         <v>0</v>
       </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -32617,6 +32924,9 @@
       <c r="I87" t="n">
         <v>0</v>
       </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -32646,6 +32956,9 @@
       <c r="I88" t="n">
         <v>0</v>
       </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -32675,6 +32988,9 @@
       <c r="I89" t="n">
         <v>0</v>
       </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -32699,9 +33015,12 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32733,6 +33052,9 @@
       <c r="I91" t="n">
         <v>0</v>
       </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -32762,6 +33084,9 @@
       <c r="I92" t="n">
         <v>0</v>
       </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -32791,6 +33116,9 @@
       <c r="I93" t="n">
         <v>0</v>
       </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -32820,6 +33148,9 @@
       <c r="I94" t="n">
         <v>0</v>
       </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -32849,6 +33180,9 @@
       <c r="I95" t="n">
         <v>0</v>
       </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -32878,6 +33212,9 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -32907,6 +33244,9 @@
       <c r="I97" t="n">
         <v>0</v>
       </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -32936,6 +33276,9 @@
       <c r="I98" t="n">
         <v>0</v>
       </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -32965,6 +33308,9 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -32994,6 +33340,9 @@
       <c r="I100" t="n">
         <v>0</v>
       </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -33023,6 +33372,9 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -33052,6 +33404,9 @@
       <c r="I102" t="n">
         <v>0</v>
       </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -33079,6 +33434,9 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
         <v>-4.547473508864641e-13</v>
       </c>
     </row>
@@ -33102,12 +33460,15 @@
         <v>-9.094947017729282e-13</v>
       </c>
       <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
       <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33139,6 +33500,9 @@
       <c r="I105" t="n">
         <v>0</v>
       </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -33168,6 +33532,9 @@
       <c r="I106" t="n">
         <v>0</v>
       </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -33197,6 +33564,9 @@
       <c r="I107" t="n">
         <v>0</v>
       </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -33226,6 +33596,9 @@
       <c r="I108" t="n">
         <v>0</v>
       </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -33255,6 +33628,9 @@
       <c r="I109" t="n">
         <v>0</v>
       </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -33284,6 +33660,9 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -33313,6 +33692,9 @@
       <c r="I111" t="n">
         <v>0</v>
       </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -33342,6 +33724,9 @@
       <c r="I112" t="n">
         <v>0</v>
       </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -33371,6 +33756,9 @@
       <c r="I113" t="n">
         <v>0</v>
       </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -33400,6 +33788,9 @@
       <c r="I114" t="n">
         <v>0</v>
       </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -33429,6 +33820,9 @@
       <c r="I115" t="n">
         <v>0</v>
       </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -33458,6 +33852,9 @@
       <c r="I116" t="n">
         <v>0</v>
       </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -33487,6 +33884,9 @@
       <c r="I117" t="n">
         <v>0</v>
       </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -33516,6 +33916,9 @@
       <c r="I118" t="n">
         <v>0</v>
       </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -33545,6 +33948,9 @@
       <c r="I119" t="n">
         <v>0</v>
       </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -33574,6 +33980,9 @@
       <c r="I120" t="n">
         <v>0</v>
       </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -33603,6 +34012,9 @@
       <c r="I121" t="n">
         <v>0</v>
       </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -33632,6 +34044,9 @@
       <c r="I122" t="n">
         <v>0</v>
       </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -33661,6 +34076,9 @@
       <c r="I123" t="n">
         <v>0</v>
       </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -33690,6 +34108,9 @@
       <c r="I124" t="n">
         <v>0</v>
       </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -33719,6 +34140,9 @@
       <c r="I125" t="n">
         <v>0</v>
       </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -33748,6 +34172,9 @@
       <c r="I126" t="n">
         <v>0</v>
       </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -33777,6 +34204,9 @@
       <c r="I127" t="n">
         <v>0</v>
       </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -33806,6 +34236,9 @@
       <c r="I128" t="n">
         <v>0</v>
       </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -33835,6 +34268,9 @@
       <c r="I129" t="n">
         <v>0</v>
       </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -33864,6 +34300,9 @@
       <c r="I130" t="n">
         <v>0</v>
       </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -33893,6 +34332,9 @@
       <c r="I131" t="n">
         <v>0</v>
       </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -33922,6 +34364,9 @@
       <c r="I132" t="n">
         <v>0</v>
       </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -33951,6 +34396,9 @@
       <c r="I133" t="n">
         <v>0</v>
       </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -33980,6 +34428,9 @@
       <c r="I134" t="n">
         <v>0</v>
       </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -34009,6 +34460,9 @@
       <c r="I135" t="n">
         <v>0</v>
       </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -34038,6 +34492,9 @@
       <c r="I136" t="n">
         <v>0</v>
       </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -34067,6 +34524,9 @@
       <c r="I137" t="n">
         <v>0</v>
       </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -34096,6 +34556,9 @@
       <c r="I138" t="n">
         <v>0</v>
       </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -34125,6 +34588,9 @@
       <c r="I139" t="n">
         <v>0</v>
       </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -34154,6 +34620,9 @@
       <c r="I140" t="n">
         <v>0</v>
       </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -34183,6 +34652,9 @@
       <c r="I141" t="n">
         <v>0</v>
       </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -34204,12 +34676,15 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
       <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34241,6 +34716,9 @@
       <c r="I143" t="n">
         <v>0</v>
       </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -34270,6 +34748,9 @@
       <c r="I144" t="n">
         <v>0</v>
       </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -34299,6 +34780,9 @@
       <c r="I145" t="n">
         <v>0</v>
       </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -34328,6 +34812,9 @@
       <c r="I146" t="n">
         <v>0</v>
       </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -34357,6 +34844,9 @@
       <c r="I147" t="n">
         <v>0</v>
       </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -34386,6 +34876,9 @@
       <c r="I148" t="n">
         <v>0</v>
       </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -34415,6 +34908,9 @@
       <c r="I149" t="n">
         <v>0</v>
       </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -34444,6 +34940,9 @@
       <c r="I150" t="n">
         <v>0</v>
       </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -34473,6 +34972,9 @@
       <c r="I151" t="n">
         <v>0</v>
       </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -34502,6 +35004,9 @@
       <c r="I152" t="n">
         <v>0</v>
       </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -34531,6 +35036,9 @@
       <c r="I153" t="n">
         <v>0</v>
       </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -34560,6 +35068,9 @@
       <c r="I154" t="n">
         <v>0</v>
       </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -34589,6 +35100,9 @@
       <c r="I155" t="n">
         <v>0</v>
       </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -34618,6 +35132,9 @@
       <c r="I156" t="n">
         <v>0</v>
       </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -34647,6 +35164,9 @@
       <c r="I157" t="n">
         <v>0</v>
       </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -34676,6 +35196,9 @@
       <c r="I158" t="n">
         <v>0</v>
       </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -34705,6 +35228,9 @@
       <c r="I159" t="n">
         <v>0</v>
       </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -34734,6 +35260,9 @@
       <c r="I160" t="n">
         <v>0</v>
       </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -34763,6 +35292,9 @@
       <c r="I161" t="n">
         <v>0</v>
       </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -34792,6 +35324,9 @@
       <c r="I162" t="n">
         <v>0</v>
       </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -34821,6 +35356,9 @@
       <c r="I163" t="n">
         <v>0</v>
       </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -34850,6 +35388,9 @@
       <c r="I164" t="n">
         <v>0</v>
       </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -34879,6 +35420,9 @@
       <c r="I165" t="n">
         <v>0</v>
       </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -34908,6 +35452,9 @@
       <c r="I166" t="n">
         <v>0</v>
       </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -34937,6 +35484,9 @@
       <c r="I167" t="n">
         <v>0</v>
       </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -34966,6 +35516,9 @@
       <c r="I168" t="n">
         <v>0</v>
       </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -34993,6 +35546,9 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35007,7 +35563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35071,6 +35627,11 @@
           <t>FR_hydrogen_bus</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>MA_hydrogen_bus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -35111,6 +35672,9 @@
       </c>
       <c r="M2" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -35153,6 +35717,9 @@
       <c r="M3" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N3" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -35194,6 +35761,9 @@
       <c r="M4" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N4" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -35235,6 +35805,9 @@
       <c r="M5" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -35276,6 +35849,9 @@
       <c r="M6" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -35317,6 +35893,9 @@
       <c r="M7" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -35358,6 +35937,9 @@
       <c r="M8" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -35399,6 +35981,9 @@
       <c r="M9" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N9" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -35440,6 +36025,9 @@
       <c r="M10" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -35481,6 +36069,9 @@
       <c r="M11" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N11" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -35522,6 +36113,9 @@
       <c r="M12" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N12" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -35563,6 +36157,9 @@
       <c r="M13" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N13" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -35604,6 +36201,9 @@
       <c r="M14" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N14" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -35645,6 +36245,9 @@
       <c r="M15" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -35686,6 +36289,9 @@
       <c r="M16" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -35727,6 +36333,9 @@
       <c r="M17" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -35768,6 +36377,9 @@
       <c r="M18" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N18" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -35809,6 +36421,9 @@
       <c r="M19" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N19" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -35850,6 +36465,9 @@
       <c r="M20" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N20" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -35891,6 +36509,9 @@
       <c r="M21" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N21" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -35932,6 +36553,9 @@
       <c r="M22" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N22" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -35973,6 +36597,9 @@
       <c r="M23" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N23" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -36014,6 +36641,9 @@
       <c r="M24" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N24" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -36055,6 +36685,9 @@
       <c r="M25" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N25" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -36096,6 +36729,9 @@
       <c r="M26" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N26" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -36137,6 +36773,9 @@
       <c r="M27" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N27" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -36178,6 +36817,9 @@
       <c r="M28" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N28" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -36219,6 +36861,9 @@
       <c r="M29" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N29" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -36260,6 +36905,9 @@
       <c r="M30" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N30" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -36301,6 +36949,9 @@
       <c r="M31" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N31" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -36342,6 +36993,9 @@
       <c r="M32" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N32" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -36383,6 +37037,9 @@
       <c r="M33" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N33" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -36424,6 +37081,9 @@
       <c r="M34" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N34" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -36465,6 +37125,9 @@
       <c r="M35" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N35" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -36506,6 +37169,9 @@
       <c r="M36" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N36" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -36547,6 +37213,9 @@
       <c r="M37" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N37" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -36588,6 +37257,9 @@
       <c r="M38" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N38" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -36629,6 +37301,9 @@
       <c r="M39" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N39" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -36670,6 +37345,9 @@
       <c r="M40" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N40" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -36711,6 +37389,9 @@
       <c r="M41" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N41" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -36752,6 +37433,9 @@
       <c r="M42" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N42" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -36793,6 +37477,9 @@
       <c r="M43" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N43" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -36834,6 +37521,9 @@
       <c r="M44" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N44" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -36875,6 +37565,9 @@
       <c r="M45" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N45" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -36916,6 +37609,9 @@
       <c r="M46" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N46" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -36957,6 +37653,9 @@
       <c r="M47" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N47" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -36998,6 +37697,9 @@
       <c r="M48" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N48" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -37039,6 +37741,9 @@
       <c r="M49" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N49" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -37080,6 +37785,9 @@
       <c r="M50" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N50" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -37121,6 +37829,9 @@
       <c r="M51" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N51" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -37162,6 +37873,9 @@
       <c r="M52" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N52" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -37203,6 +37917,9 @@
       <c r="M53" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N53" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -37244,6 +37961,9 @@
       <c r="M54" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N54" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -37285,6 +38005,9 @@
       <c r="M55" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N55" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -37326,6 +38049,9 @@
       <c r="M56" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N56" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -37367,6 +38093,9 @@
       <c r="M57" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N57" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -37408,6 +38137,9 @@
       <c r="M58" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N58" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -37449,6 +38181,9 @@
       <c r="M59" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N59" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -37490,6 +38225,9 @@
       <c r="M60" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N60" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -37531,6 +38269,9 @@
       <c r="M61" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N61" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -37572,6 +38313,9 @@
       <c r="M62" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N62" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -37613,6 +38357,9 @@
       <c r="M63" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N63" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -37654,6 +38401,9 @@
       <c r="M64" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N64" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -37695,6 +38445,9 @@
       <c r="M65" t="n">
         <v>7.194139194139193</v>
       </c>
+      <c r="N65" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -37736,6 +38489,9 @@
       <c r="M66" t="n">
         <v>7.194139194139193</v>
       </c>
+      <c r="N66" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -37777,6 +38533,9 @@
       <c r="M67" t="n">
         <v>7.194139194139193</v>
       </c>
+      <c r="N67" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -37818,6 +38577,9 @@
       <c r="M68" t="n">
         <v>5.292952361116891</v>
       </c>
+      <c r="N68" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -37859,6 +38621,9 @@
       <c r="M69" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N69" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -37880,7 +38645,7 @@
         <v>0.01</v>
       </c>
       <c r="G70" t="n">
-        <v>67.46666666666667</v>
+        <v>67.46666666666665</v>
       </c>
       <c r="H70" t="n">
         <v>53.34666666666666</v>
@@ -37889,7 +38654,7 @@
         <v>-0</v>
       </c>
       <c r="J70" t="n">
-        <v>67.46666666666667</v>
+        <v>67.46666666666665</v>
       </c>
       <c r="K70" t="n">
         <v>-0</v>
@@ -37899,6 +38664,9 @@
       </c>
       <c r="M70" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="71">
@@ -37941,6 +38709,9 @@
       <c r="M71" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N71" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -37982,6 +38753,9 @@
       <c r="M72" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N72" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -38023,6 +38797,9 @@
       <c r="M73" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N73" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -38064,6 +38841,9 @@
       <c r="M74" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N74" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -38105,6 +38885,9 @@
       <c r="M75" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N75" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -38126,7 +38909,7 @@
         <v>0.01</v>
       </c>
       <c r="G76" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="H76" t="n">
         <v>53.34666666666666</v>
@@ -38135,7 +38918,7 @@
         <v>-0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="K76" t="n">
         <v>-0</v>
@@ -38145,6 +38928,9 @@
       </c>
       <c r="M76" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="77">
@@ -38187,6 +38973,9 @@
       <c r="M77" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N77" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -38228,6 +39017,9 @@
       <c r="M78" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N78" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -38249,7 +39041,7 @@
         <v>0.01</v>
       </c>
       <c r="G79" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="H79" t="n">
         <v>53.34666666666666</v>
@@ -38258,7 +39050,7 @@
         <v>-0</v>
       </c>
       <c r="J79" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="K79" t="n">
         <v>-0</v>
@@ -38268,6 +39060,9 @@
       </c>
       <c r="M79" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="80">
@@ -38290,7 +39085,7 @@
         <v>0.01</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="H80" t="n">
         <v>53.34666666666666</v>
@@ -38299,7 +39094,7 @@
         <v>-0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="K80" t="n">
         <v>-0</v>
@@ -38309,6 +39104,9 @@
       </c>
       <c r="M80" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="81">
@@ -38351,6 +39149,9 @@
       <c r="M81" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N81" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -38372,7 +39173,7 @@
         <v>0.01</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1118147448015123</v>
+        <v>0.1118147448015155</v>
       </c>
       <c r="H82" t="n">
         <v>53.34666666666666</v>
@@ -38381,7 +39182,7 @@
         <v>-0</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1118147448015123</v>
+        <v>0.1118147448015155</v>
       </c>
       <c r="K82" t="n">
         <v>-0</v>
@@ -38391,6 +39192,9 @@
       </c>
       <c r="M82" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="83">
@@ -38413,7 +39217,7 @@
         <v>0.01</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1118147448015123</v>
+        <v>0.1118147448015155</v>
       </c>
       <c r="H83" t="n">
         <v>53.34666666666666</v>
@@ -38422,7 +39226,7 @@
         <v>-0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1118147448015123</v>
+        <v>0.1118147448015155</v>
       </c>
       <c r="K83" t="n">
         <v>-0</v>
@@ -38432,6 +39236,9 @@
       </c>
       <c r="M83" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="84">
@@ -38454,7 +39261,7 @@
         <v>0.01</v>
       </c>
       <c r="G84" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="H84" t="n">
         <v>53.34666666666666</v>
@@ -38463,7 +39270,7 @@
         <v>-0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.01</v>
+        <v>0.01000000000000274</v>
       </c>
       <c r="K84" t="n">
         <v>-0</v>
@@ -38473,6 +39280,9 @@
       </c>
       <c r="M84" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="85">
@@ -38515,6 +39325,9 @@
       <c r="M85" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N85" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -38556,6 +39369,9 @@
       <c r="M86" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N86" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -38597,6 +39413,9 @@
       <c r="M87" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N87" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -38638,6 +39457,9 @@
       <c r="M88" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N88" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -38679,6 +39501,9 @@
       <c r="M89" t="n">
         <v>7.194139194139193</v>
       </c>
+      <c r="N89" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -38720,6 +39545,9 @@
       <c r="M90" t="n">
         <v>7.194139194139193</v>
       </c>
+      <c r="N90" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -38761,6 +39589,9 @@
       <c r="M91" t="n">
         <v>103.980463980464</v>
       </c>
+      <c r="N91" t="n">
+        <v>91.38095238095239</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -38802,6 +39633,9 @@
       <c r="M92" t="n">
         <v>103.980463980464</v>
       </c>
+      <c r="N92" t="n">
+        <v>91.38095238095239</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -38843,6 +39677,9 @@
       <c r="M93" t="n">
         <v>103.980463980464</v>
       </c>
+      <c r="N93" t="n">
+        <v>91.38095238095239</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -38884,6 +39721,9 @@
       <c r="M94" t="n">
         <v>10.387902695595</v>
       </c>
+      <c r="N94" t="n">
+        <v>0.1282051282051278</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -38925,6 +39765,9 @@
       <c r="M95" t="n">
         <v>7.194139194139193</v>
       </c>
+      <c r="N95" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -38966,6 +39809,9 @@
       <c r="M96" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N96" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -39007,6 +39853,9 @@
       <c r="M97" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N97" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -39048,6 +39897,9 @@
       <c r="M98" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N98" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -39089,6 +39941,9 @@
       <c r="M99" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N99" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -39130,6 +39985,9 @@
       <c r="M100" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N100" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -39171,6 +40029,9 @@
       <c r="M101" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N101" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -39212,6 +40073,9 @@
       <c r="M102" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N102" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -39253,6 +40117,9 @@
       <c r="M103" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N103" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -39294,6 +40161,9 @@
       <c r="M104" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N104" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -39335,6 +40205,9 @@
       <c r="M105" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N105" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -39376,6 +40249,9 @@
       <c r="M106" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N106" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -39417,6 +40293,9 @@
       <c r="M107" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N107" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -39458,6 +40337,9 @@
       <c r="M108" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N108" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -39499,6 +40381,9 @@
       <c r="M109" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N109" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -39540,6 +40425,9 @@
       <c r="M110" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N110" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -39581,6 +40469,9 @@
       <c r="M111" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N111" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -39622,6 +40513,9 @@
       <c r="M112" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N112" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -39663,6 +40557,9 @@
       <c r="M113" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N113" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -39704,6 +40601,9 @@
       <c r="M114" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N114" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -39745,6 +40645,9 @@
       <c r="M115" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N115" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -39786,6 +40689,9 @@
       <c r="M116" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N116" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -39827,6 +40733,9 @@
       <c r="M117" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N117" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -39868,6 +40777,9 @@
       <c r="M118" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N118" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -39909,6 +40821,9 @@
       <c r="M119" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N119" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -39950,6 +40865,9 @@
       <c r="M120" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N120" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -39991,6 +40909,9 @@
       <c r="M121" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N121" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -40032,6 +40953,9 @@
       <c r="M122" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N122" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -40073,6 +40997,9 @@
       <c r="M123" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N123" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -40114,6 +41041,9 @@
       <c r="M124" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N124" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -40155,6 +41085,9 @@
       <c r="M125" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N125" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -40196,6 +41129,9 @@
       <c r="M126" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N126" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -40237,6 +41173,9 @@
       <c r="M127" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N127" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -40278,6 +41217,9 @@
       <c r="M128" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N128" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -40319,6 +41261,9 @@
       <c r="M129" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N129" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -40360,6 +41305,9 @@
       <c r="M130" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N130" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -40401,6 +41349,9 @@
       <c r="M131" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N131" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -40442,6 +41393,9 @@
       <c r="M132" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N132" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -40483,6 +41437,9 @@
       <c r="M133" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N133" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -40524,6 +41481,9 @@
       <c r="M134" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N134" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -40565,6 +41525,9 @@
       <c r="M135" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N135" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -40606,6 +41569,9 @@
       <c r="M136" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N136" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -40647,6 +41613,9 @@
       <c r="M137" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N137" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -40688,6 +41657,9 @@
       <c r="M138" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N138" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -40729,6 +41701,9 @@
       <c r="M139" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N139" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -40770,6 +41745,9 @@
       <c r="M140" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N140" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -40791,7 +41769,7 @@
         <v>0.01</v>
       </c>
       <c r="G141" t="n">
-        <v>67.46666666666665</v>
+        <v>67.46666666666667</v>
       </c>
       <c r="H141" t="n">
         <v>53.34666666666666</v>
@@ -40800,7 +41778,7 @@
         <v>-0</v>
       </c>
       <c r="J141" t="n">
-        <v>67.46666666666665</v>
+        <v>67.46666666666667</v>
       </c>
       <c r="K141" t="n">
         <v>-0</v>
@@ -40810,6 +41788,9 @@
       </c>
       <c r="M141" t="n">
         <v>5.142857142857143</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="142">
@@ -40852,6 +41833,9 @@
       <c r="M142" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N142" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -40893,6 +41877,9 @@
       <c r="M143" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N143" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -40934,6 +41921,9 @@
       <c r="M144" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N144" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -40975,6 +41965,9 @@
       <c r="M145" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N145" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -41016,6 +42009,9 @@
       <c r="M146" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N146" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -41057,6 +42053,9 @@
       <c r="M147" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N147" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -41098,6 +42097,9 @@
       <c r="M148" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N148" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -41139,6 +42141,9 @@
       <c r="M149" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N149" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -41180,6 +42185,9 @@
       <c r="M150" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N150" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -41221,6 +42229,9 @@
       <c r="M151" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N151" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -41262,6 +42273,9 @@
       <c r="M152" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N152" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -41303,6 +42317,9 @@
       <c r="M153" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N153" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -41344,6 +42361,9 @@
       <c r="M154" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N154" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -41385,6 +42405,9 @@
       <c r="M155" t="n">
         <v>5.142857142857143</v>
       </c>
+      <c r="N155" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -41426,6 +42449,9 @@
       <c r="M156" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N156" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -41467,6 +42493,9 @@
       <c r="M157" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N157" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -41508,6 +42537,9 @@
       <c r="M158" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N158" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -41549,6 +42581,9 @@
       <c r="M159" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N159" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -41590,6 +42625,9 @@
       <c r="M160" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N160" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -41631,6 +42669,9 @@
       <c r="M161" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N161" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -41672,6 +42713,9 @@
       <c r="M162" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N162" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -41713,6 +42757,9 @@
       <c r="M163" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N163" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -41754,6 +42801,9 @@
       <c r="M164" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N164" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -41795,6 +42845,9 @@
       <c r="M165" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N165" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -41836,6 +42889,9 @@
       <c r="M166" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N166" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -41877,6 +42933,9 @@
       <c r="M167" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N167" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -41918,6 +42977,9 @@
       <c r="M168" t="n">
         <v>5.142857142857141</v>
       </c>
+      <c r="N168" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -41958,6 +43020,9 @@
       </c>
       <c r="M169" t="n">
         <v>5.142857142857141</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -42312,7 +43377,7 @@
         <v>-0</v>
       </c>
       <c r="C17" t="n">
-        <v>-2877.75</v>
+        <v>-631.9590009571984</v>
       </c>
     </row>
     <row r="18">
@@ -42496,7 +43561,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>-2023.069379329681</v>
+        <v>-9990.5629747239</v>
       </c>
       <c r="C34" t="n">
         <v>-0</v>
@@ -42947,7 +44012,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>-9990.5629747239</v>
+        <v>-0</v>
       </c>
       <c r="C75" t="n">
         <v>-429.5968808020002</v>
@@ -42961,7 +44026,7 @@
         <v>-0</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1225.763316321416</v>
       </c>
     </row>
     <row r="77">
@@ -42994,7 +44059,7 @@
         <v>-0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1446.107778251606</v>
       </c>
     </row>
     <row r="80">
@@ -43071,7 +44136,7 @@
         <v>-0</v>
       </c>
       <c r="C86" t="n">
-        <v>-426.0800955318846</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="87">
@@ -43115,7 +44180,7 @@
         <v>-0</v>
       </c>
       <c r="C90" t="n">
-        <v>5335.108485979174</v>
+        <v>3678.418319851702</v>
       </c>
     </row>
     <row r="91">
@@ -43159,7 +44224,7 @@
         <v>-0</v>
       </c>
       <c r="C94" t="n">
-        <v>5009.729374738103</v>
+        <v>6666.419540865573</v>
       </c>
     </row>
     <row r="95">
@@ -43687,7 +44752,7 @@
         <v>-0</v>
       </c>
       <c r="C142" t="n">
-        <v>827.3361998509694</v>
+        <v>827.3361998509695</v>
       </c>
     </row>
     <row r="143">
@@ -43904,7 +44969,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>-0</v>
+        <v>-2023.069379329681</v>
       </c>
       <c r="C162" t="n">
         <v>-0</v>
@@ -44018,10 +45083,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C2" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="3">
@@ -44029,10 +45094,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C3" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="4">
@@ -44040,10 +45105,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C4" t="n">
-        <v>687332.4224274274</v>
+        <v>2947274.041707798</v>
       </c>
     </row>
     <row r="5">
@@ -44051,10 +45116,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C5" t="n">
-        <v>689073.3325803705</v>
+        <v>2949014.951860741</v>
       </c>
     </row>
     <row r="6">
@@ -44062,10 +45127,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C6" t="n">
-        <v>691496.8791087781</v>
+        <v>2951438.498389149</v>
       </c>
     </row>
     <row r="7">
@@ -44073,10 +45138,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C7" t="n">
-        <v>693992.581113801</v>
+        <v>2953934.200394172</v>
       </c>
     </row>
     <row r="8">
@@ -44084,10 +45149,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C8" t="n">
-        <v>696014.9057277665</v>
+        <v>2955956.525008138</v>
       </c>
     </row>
     <row r="9">
@@ -44095,10 +45160,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C9" t="n">
-        <v>696014.9057277665</v>
+        <v>2955956.525008138</v>
       </c>
     </row>
     <row r="10">
@@ -44106,10 +45171,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C10" t="n">
-        <v>698892.6557277665</v>
+        <v>2958834.275008138</v>
       </c>
     </row>
     <row r="11">
@@ -44117,10 +45182,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C11" t="n">
-        <v>701770.4057277665</v>
+        <v>2961712.025008138</v>
       </c>
     </row>
     <row r="12">
@@ -44128,10 +45193,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C12" t="n">
-        <v>704648.1557277665</v>
+        <v>2964589.775008138</v>
       </c>
     </row>
     <row r="13">
@@ -44139,10 +45204,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C13" t="n">
-        <v>707525.9057277665</v>
+        <v>2967467.525008138</v>
       </c>
     </row>
     <row r="14">
@@ -44150,10 +45215,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C14" t="n">
-        <v>710403.6557277665</v>
+        <v>2970345.275008138</v>
       </c>
     </row>
     <row r="15">
@@ -44161,10 +45226,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C15" t="n">
-        <v>713281.4057277665</v>
+        <v>2973223.025008138</v>
       </c>
     </row>
     <row r="16">
@@ -44172,10 +45237,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C16" t="n">
-        <v>716159.1557277665</v>
+        <v>2976100.775008138</v>
       </c>
     </row>
     <row r="17">
@@ -44183,10 +45248,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C17" t="n">
-        <v>719036.9057277665</v>
+        <v>2976732.734009095</v>
       </c>
     </row>
     <row r="18">
@@ -44194,10 +45259,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C18" t="n">
-        <v>719036.9057277665</v>
+        <v>2976732.734009095</v>
       </c>
     </row>
     <row r="19">
@@ -44205,10 +45270,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C19" t="n">
-        <v>711432.0057277664</v>
+        <v>2969127.834009095</v>
       </c>
     </row>
     <row r="20">
@@ -44216,10 +45281,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C20" t="n">
-        <v>703827.1057277664</v>
+        <v>2961522.934009095</v>
       </c>
     </row>
     <row r="21">
@@ -44227,10 +45292,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C21" t="n">
-        <v>696222.2057277664</v>
+        <v>2953918.034009095</v>
       </c>
     </row>
     <row r="22">
@@ -44238,10 +45303,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C22" t="n">
-        <v>688617.3057277664</v>
+        <v>2946313.134009095</v>
       </c>
     </row>
     <row r="23">
@@ -44249,10 +45314,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C23" t="n">
-        <v>681012.4057277663</v>
+        <v>2938708.234009095</v>
       </c>
     </row>
     <row r="24">
@@ -44260,10 +45325,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C24" t="n">
-        <v>673407.5057277663</v>
+        <v>2931103.334009096</v>
       </c>
     </row>
     <row r="25">
@@ -44271,10 +45336,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C25" t="n">
-        <v>665802.6057277663</v>
+        <v>2923498.434009096</v>
       </c>
     </row>
     <row r="26">
@@ -44282,10 +45347,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C26" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="27">
@@ -44293,10 +45358,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C27" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="28">
@@ -44304,10 +45369,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C28" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="29">
@@ -44315,10 +45380,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C29" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="30">
@@ -44326,10 +45391,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C30" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="31">
@@ -44337,10 +45402,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C31" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="32">
@@ -44348,10 +45413,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C32" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="33">
@@ -44359,10 +45424,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C33" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="34">
@@ -44370,10 +45435,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C34" t="n">
-        <v>661520</v>
+        <v>2919215.828281329</v>
       </c>
     </row>
     <row r="35">
@@ -44381,10 +45446,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C35" t="n">
-        <v>664397.75</v>
+        <v>2922093.578281329</v>
       </c>
     </row>
     <row r="36">
@@ -44392,10 +45457,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C36" t="n">
-        <v>667275.5</v>
+        <v>2924971.328281329</v>
       </c>
     </row>
     <row r="37">
@@ -44403,10 +45468,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C37" t="n">
-        <v>667275.5</v>
+        <v>2924971.328281329</v>
       </c>
     </row>
     <row r="38">
@@ -44414,10 +45479,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C38" t="n">
-        <v>667275.5</v>
+        <v>2924971.328281329</v>
       </c>
     </row>
     <row r="39">
@@ -44425,10 +45490,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C39" t="n">
-        <v>670153.25</v>
+        <v>2927849.078281329</v>
       </c>
     </row>
     <row r="40">
@@ -44436,10 +45501,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C40" t="n">
-        <v>673031</v>
+        <v>2930726.828281329</v>
       </c>
     </row>
     <row r="41">
@@ -44447,10 +45512,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C41" t="n">
-        <v>673031</v>
+        <v>2930726.828281329</v>
       </c>
     </row>
     <row r="42">
@@ -44458,10 +45523,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C42" t="n">
-        <v>673031</v>
+        <v>2930726.828281329</v>
       </c>
     </row>
     <row r="43">
@@ -44469,10 +45534,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C43" t="n">
-        <v>671286.8784328923</v>
+        <v>2928982.706714222</v>
       </c>
     </row>
     <row r="44">
@@ -44480,10 +45545,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>277538823.0693793</v>
+        <v>277548813.6323541</v>
       </c>
       <c r="C44" t="n">
-        <v>671286.8784328923</v>
+        <v>2928982.706714222</v>
       </c>
     </row>
     <row r="45">
@@ -44491,10 +45556,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C45" t="n">
-        <v>671286.8784328923</v>
+        <v>2928982.706714222</v>
       </c>
     </row>
     <row r="46">
@@ -44502,10 +45567,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C46" t="n">
-        <v>671286.8784328923</v>
+        <v>2928982.706714222</v>
       </c>
     </row>
     <row r="47">
@@ -44513,10 +45578,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C47" t="n">
-        <v>671286.8784328923</v>
+        <v>2928982.706714222</v>
       </c>
     </row>
     <row r="48">
@@ -44524,10 +45589,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C48" t="n">
-        <v>671479.2934004032</v>
+        <v>2929175.121681733</v>
       </c>
     </row>
     <row r="49">
@@ -44535,10 +45600,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C49" t="n">
-        <v>673276.1393532639</v>
+        <v>2930971.967634593</v>
       </c>
     </row>
     <row r="50">
@@ -44546,10 +45611,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C50" t="n">
-        <v>676153.8893532639</v>
+        <v>2933849.717634593</v>
       </c>
     </row>
     <row r="51">
@@ -44557,10 +45622,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C51" t="n">
-        <v>679031.6393532639</v>
+        <v>2936727.467634593</v>
       </c>
     </row>
     <row r="52">
@@ -44568,10 +45633,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C52" t="n">
-        <v>679031.6393532639</v>
+        <v>2936727.467634593</v>
       </c>
     </row>
     <row r="53">
@@ -44579,10 +45644,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C53" t="n">
-        <v>681909.3893532639</v>
+        <v>2939605.217634593</v>
       </c>
     </row>
     <row r="54">
@@ -44590,10 +45655,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C54" t="n">
-        <v>684787.1393532639</v>
+        <v>2942482.967634593</v>
       </c>
     </row>
     <row r="55">
@@ -44601,10 +45666,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C55" t="n">
-        <v>687664.8893532639</v>
+        <v>2945360.717634593</v>
       </c>
     </row>
     <row r="56">
@@ -44612,10 +45677,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C56" t="n">
-        <v>690542.6393532639</v>
+        <v>2948238.467634593</v>
       </c>
     </row>
     <row r="57">
@@ -44623,10 +45688,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C57" t="n">
-        <v>691363.6262378637</v>
+        <v>2949059.454519193</v>
       </c>
     </row>
     <row r="58">
@@ -44634,10 +45699,10 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C58" t="n">
-        <v>691523.7588293212</v>
+        <v>2949219.58711065</v>
       </c>
     </row>
     <row r="59">
@@ -44645,10 +45710,10 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C59" t="n">
-        <v>694401.5088293212</v>
+        <v>2952097.33711065</v>
       </c>
     </row>
     <row r="60">
@@ -44656,10 +45721,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C60" t="n">
-        <v>697279.2588293212</v>
+        <v>2954975.08711065</v>
       </c>
     </row>
     <row r="61">
@@ -44667,10 +45732,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C61" t="n">
-        <v>700157.0088293212</v>
+        <v>2957852.83711065</v>
       </c>
     </row>
     <row r="62">
@@ -44678,10 +45743,10 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C62" t="n">
-        <v>703034.7588293212</v>
+        <v>2960730.58711065</v>
       </c>
     </row>
     <row r="63">
@@ -44689,10 +45754,10 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C63" t="n">
-        <v>705912.5088293212</v>
+        <v>2963608.33711065</v>
       </c>
     </row>
     <row r="64">
@@ -44700,10 +45765,10 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C64" t="n">
-        <v>708790.2588293212</v>
+        <v>2966486.08711065</v>
       </c>
     </row>
     <row r="65">
@@ -44711,10 +45776,10 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C65" t="n">
-        <v>711668.0088293212</v>
+        <v>2969363.83711065</v>
       </c>
     </row>
     <row r="66">
@@ -44722,10 +45787,10 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C66" t="n">
-        <v>711668.0088293212</v>
+        <v>2969363.83711065</v>
       </c>
     </row>
     <row r="67">
@@ -44733,10 +45798,10 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C67" t="n">
-        <v>706349.5587654371</v>
+        <v>2964045.387046766</v>
       </c>
     </row>
     <row r="68">
@@ -44744,10 +45809,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C68" t="n">
-        <v>703275.8008206078</v>
+        <v>2960971.629101937</v>
       </c>
     </row>
     <row r="69">
@@ -44755,10 +45820,10 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C69" t="n">
-        <v>702248.5890914929</v>
+        <v>2959944.417372822</v>
       </c>
     </row>
     <row r="70">
@@ -44766,10 +45831,10 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C70" t="n">
-        <v>702248.5890914929</v>
+        <v>2959944.417372822</v>
       </c>
     </row>
     <row r="71">
@@ -44777,10 +45842,10 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C71" t="n">
-        <v>702248.5890914929</v>
+        <v>2959944.417372822</v>
       </c>
     </row>
     <row r="72">
@@ -44788,10 +45853,10 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C72" t="n">
-        <v>702248.5890914929</v>
+        <v>2959944.417372822</v>
       </c>
     </row>
     <row r="73">
@@ -44799,10 +45864,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C73" t="n">
-        <v>702248.5890914929</v>
+        <v>2959944.417372822</v>
       </c>
     </row>
     <row r="74">
@@ -44810,10 +45875,10 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>277548813.6323541</v>
+        <v>277558804.1953288</v>
       </c>
       <c r="C74" t="n">
-        <v>702248.5890914929</v>
+        <v>2959944.417372822</v>
       </c>
     </row>
     <row r="75">
@@ -44824,7 +45889,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C75" t="n">
-        <v>702678.1859722949</v>
+        <v>2960374.014253624</v>
       </c>
     </row>
     <row r="76">
@@ -44835,7 +45900,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C76" t="n">
-        <v>702678.1859722949</v>
+        <v>2961599.777569945</v>
       </c>
     </row>
     <row r="77">
@@ -44846,7 +45911,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C77" t="n">
-        <v>704067.3383002861</v>
+        <v>2962988.929897936</v>
       </c>
     </row>
     <row r="78">
@@ -44857,7 +45922,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C78" t="n">
-        <v>705987.9690306005</v>
+        <v>2964909.56062825</v>
       </c>
     </row>
     <row r="79">
@@ -44868,7 +45933,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C79" t="n">
-        <v>705987.9690306005</v>
+        <v>2966355.668406502</v>
       </c>
     </row>
     <row r="80">
@@ -44879,7 +45944,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C80" t="n">
-        <v>705987.9690306005</v>
+        <v>2966355.668406502</v>
       </c>
     </row>
     <row r="81">
@@ -44890,7 +45955,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C81" t="n">
-        <v>706776.6915564499</v>
+        <v>2967144.390932351</v>
       </c>
     </row>
     <row r="82">
@@ -44901,7 +45966,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C82" t="n">
-        <v>706776.6915564499</v>
+        <v>2967144.390932351</v>
       </c>
     </row>
     <row r="83">
@@ -44912,7 +45977,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C83" t="n">
-        <v>706776.6915564499</v>
+        <v>2967144.390932351</v>
       </c>
     </row>
     <row r="84">
@@ -44923,7 +45988,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C84" t="n">
-        <v>709654.4415564499</v>
+        <v>2970022.140932351</v>
       </c>
     </row>
     <row r="85">
@@ -44934,7 +45999,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C85" t="n">
-        <v>709654.4415564499</v>
+        <v>2970022.140932351</v>
       </c>
     </row>
     <row r="86">
@@ -44945,7 +46010,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C86" t="n">
-        <v>710080.5216519817</v>
+        <v>2970022.140932351</v>
       </c>
     </row>
     <row r="87">
@@ -44956,7 +46021,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C87" t="n">
-        <v>712958.2716519817</v>
+        <v>2972899.890932351</v>
       </c>
     </row>
     <row r="88">
@@ -44967,7 +46032,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C88" t="n">
-        <v>715836.0216519817</v>
+        <v>2975777.640932351</v>
       </c>
     </row>
     <row r="89">
@@ -44978,7 +46043,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C89" t="n">
-        <v>715836.0216519817</v>
+        <v>2975777.640932351</v>
       </c>
     </row>
     <row r="90">
@@ -44989,7 +46054,7 @@
         <v>277558804.1953288</v>
       </c>
       <c r="C90" t="n">
-        <v>710500.9131660026</v>
+        <v>2972099.2226125</v>
       </c>
     </row>
     <row r="91">
@@ -45000,7 +46065,7 @@
         <v>277549542.5809418</v>
       </c>
       <c r="C91" t="n">
-        <v>702896.0131660026</v>
+        <v>2964494.3226125</v>
       </c>
     </row>
     <row r="92">
@@ -45011,7 +46076,7 @@
         <v>277538506.6742288</v>
       </c>
       <c r="C92" t="n">
-        <v>695291.1131660026</v>
+        <v>2956889.4226125</v>
       </c>
     </row>
     <row r="93">
@@ -45022,7 +46087,7 @@
         <v>277536800</v>
       </c>
       <c r="C93" t="n">
-        <v>688673.6592051077</v>
+        <v>2950271.968651605</v>
       </c>
     </row>
     <row r="94">
@@ -45033,7 +46098,7 @@
         <v>277536800</v>
       </c>
       <c r="C94" t="n">
-        <v>683663.9298303697</v>
+        <v>2943605.54911074</v>
       </c>
     </row>
     <row r="95">
@@ -45044,7 +46109,7 @@
         <v>277536800</v>
       </c>
       <c r="C95" t="n">
-        <v>683663.9298303697</v>
+        <v>2943605.54911074</v>
       </c>
     </row>
     <row r="96">
@@ -45055,7 +46120,7 @@
         <v>277536800</v>
       </c>
       <c r="C96" t="n">
-        <v>683663.9298303697</v>
+        <v>2943605.54911074</v>
       </c>
     </row>
     <row r="97">
@@ -45066,7 +46131,7 @@
         <v>277536800</v>
       </c>
       <c r="C97" t="n">
-        <v>683663.9298303697</v>
+        <v>2943605.54911074</v>
       </c>
     </row>
     <row r="98">
@@ -45077,7 +46142,7 @@
         <v>277536800</v>
       </c>
       <c r="C98" t="n">
-        <v>683794.3982879325</v>
+        <v>2943736.017568303</v>
       </c>
     </row>
     <row r="99">
@@ -45088,7 +46153,7 @@
         <v>277536800</v>
       </c>
       <c r="C99" t="n">
-        <v>686020.4675249081</v>
+        <v>2945962.086805278</v>
       </c>
     </row>
     <row r="100">
@@ -45099,7 +46164,7 @@
         <v>277536800</v>
       </c>
       <c r="C100" t="n">
-        <v>688898.2175249081</v>
+        <v>2948839.836805278</v>
       </c>
     </row>
     <row r="101">
@@ -45110,7 +46175,7 @@
         <v>277536800</v>
       </c>
       <c r="C101" t="n">
-        <v>691775.9675249081</v>
+        <v>2951717.586805278</v>
       </c>
     </row>
     <row r="102">
@@ -45121,7 +46186,7 @@
         <v>277536800</v>
       </c>
       <c r="C102" t="n">
-        <v>694653.7175249081</v>
+        <v>2954595.336805278</v>
       </c>
     </row>
     <row r="103">
@@ -45132,7 +46197,7 @@
         <v>277536800</v>
       </c>
       <c r="C103" t="n">
-        <v>697531.4675249081</v>
+        <v>2957473.086805278</v>
       </c>
     </row>
     <row r="104">
@@ -45143,7 +46208,7 @@
         <v>277536800</v>
       </c>
       <c r="C104" t="n">
-        <v>700409.2175249081</v>
+        <v>2960350.836805278</v>
       </c>
     </row>
     <row r="105">
@@ -45154,7 +46219,7 @@
         <v>277536800</v>
       </c>
       <c r="C105" t="n">
-        <v>702509.6307196296</v>
+        <v>2962451.25</v>
       </c>
     </row>
     <row r="106">
@@ -45165,7 +46230,7 @@
         <v>277536800</v>
       </c>
       <c r="C106" t="n">
-        <v>705387.3807196296</v>
+        <v>2965329</v>
       </c>
     </row>
     <row r="107">
@@ -45176,7 +46241,7 @@
         <v>277536800</v>
       </c>
       <c r="C107" t="n">
-        <v>708265.1307196296</v>
+        <v>2968206.75</v>
       </c>
     </row>
     <row r="108">
@@ -45187,7 +46252,7 @@
         <v>277536800</v>
       </c>
       <c r="C108" t="n">
-        <v>708265.1307196296</v>
+        <v>2968206.75</v>
       </c>
     </row>
     <row r="109">
@@ -45198,7 +46263,7 @@
         <v>277536800</v>
       </c>
       <c r="C109" t="n">
-        <v>708265.1307196296</v>
+        <v>2968206.75</v>
       </c>
     </row>
     <row r="110">
@@ -45209,7 +46274,7 @@
         <v>277536800</v>
       </c>
       <c r="C110" t="n">
-        <v>711142.8807196296</v>
+        <v>2971084.5</v>
       </c>
     </row>
     <row r="111">
@@ -45220,7 +46285,7 @@
         <v>277536800</v>
       </c>
       <c r="C111" t="n">
-        <v>714020.6307196296</v>
+        <v>2973962.25</v>
       </c>
     </row>
     <row r="112">
@@ -45231,7 +46296,7 @@
         <v>277536800</v>
       </c>
       <c r="C112" t="n">
-        <v>716898.3807196296</v>
+        <v>2976840</v>
       </c>
     </row>
     <row r="113">
@@ -45242,7 +46307,7 @@
         <v>277536800</v>
       </c>
       <c r="C113" t="n">
-        <v>716898.3807196296</v>
+        <v>2976840</v>
       </c>
     </row>
     <row r="114">
@@ -45253,7 +46318,7 @@
         <v>277536800</v>
       </c>
       <c r="C114" t="n">
-        <v>716898.3807196296</v>
+        <v>2976840</v>
       </c>
     </row>
     <row r="115">
@@ -45264,7 +46329,7 @@
         <v>277536800</v>
       </c>
       <c r="C115" t="n">
-        <v>709293.4807196296</v>
+        <v>2969235.1</v>
       </c>
     </row>
     <row r="116">
@@ -45275,7 +46340,7 @@
         <v>277536800</v>
       </c>
       <c r="C116" t="n">
-        <v>701688.5807196295</v>
+        <v>2961630.2</v>
       </c>
     </row>
     <row r="117">
@@ -45286,7 +46351,7 @@
         <v>277536800</v>
       </c>
       <c r="C117" t="n">
-        <v>694083.6807196295</v>
+        <v>2954025.3</v>
       </c>
     </row>
     <row r="118">
@@ -45297,7 +46362,7 @@
         <v>277536800</v>
       </c>
       <c r="C118" t="n">
-        <v>686478.7807196295</v>
+        <v>2946420.4</v>
       </c>
     </row>
     <row r="119">
@@ -45308,7 +46373,7 @@
         <v>277536800</v>
       </c>
       <c r="C119" t="n">
-        <v>678873.8807196295</v>
+        <v>2938815.5</v>
       </c>
     </row>
     <row r="120">
@@ -45319,7 +46384,7 @@
         <v>277536800</v>
       </c>
       <c r="C120" t="n">
-        <v>675561.1747418171</v>
+        <v>2935502.794022188</v>
       </c>
     </row>
     <row r="121">
@@ -45330,7 +46395,7 @@
         <v>277536800</v>
       </c>
       <c r="C121" t="n">
-        <v>675561.1747418171</v>
+        <v>2935502.794022188</v>
       </c>
     </row>
     <row r="122">
@@ -45341,7 +46406,7 @@
         <v>277536800</v>
       </c>
       <c r="C122" t="n">
-        <v>675561.1747418171</v>
+        <v>2935502.794022188</v>
       </c>
     </row>
     <row r="123">
@@ -45352,7 +46417,7 @@
         <v>277536800</v>
       </c>
       <c r="C123" t="n">
-        <v>676953.2779413948</v>
+        <v>2936894.897221766</v>
       </c>
     </row>
     <row r="124">
@@ -45363,7 +46428,7 @@
         <v>277536800</v>
       </c>
       <c r="C124" t="n">
-        <v>676953.2779413948</v>
+        <v>2936894.897221766</v>
       </c>
     </row>
     <row r="125">
@@ -45374,7 +46439,7 @@
         <v>277536800</v>
       </c>
       <c r="C125" t="n">
-        <v>679505.9556769069</v>
+        <v>2939447.574957278</v>
       </c>
     </row>
     <row r="126">
@@ -45385,7 +46450,7 @@
         <v>277536800</v>
       </c>
       <c r="C126" t="n">
-        <v>680134.6471643674</v>
+        <v>2940076.266444738</v>
       </c>
     </row>
     <row r="127">
@@ -45396,7 +46461,7 @@
         <v>277536800</v>
       </c>
       <c r="C127" t="n">
-        <v>681269.6955818302</v>
+        <v>2941211.314862201</v>
       </c>
     </row>
     <row r="128">
@@ -45407,7 +46472,7 @@
         <v>277536800</v>
       </c>
       <c r="C128" t="n">
-        <v>681269.6955818302</v>
+        <v>2941211.314862201</v>
       </c>
     </row>
     <row r="129">
@@ -45418,7 +46483,7 @@
         <v>277536800</v>
       </c>
       <c r="C129" t="n">
-        <v>681269.6955818302</v>
+        <v>2941211.314862201</v>
       </c>
     </row>
     <row r="130">
@@ -45429,7 +46494,7 @@
         <v>277536800</v>
       </c>
       <c r="C130" t="n">
-        <v>683581.4365930443</v>
+        <v>2943523.055873415</v>
       </c>
     </row>
     <row r="131">
@@ -45440,7 +46505,7 @@
         <v>277536800</v>
       </c>
       <c r="C131" t="n">
-        <v>686459.1865930443</v>
+        <v>2946400.805873415</v>
       </c>
     </row>
     <row r="132">
@@ -45451,7 +46516,7 @@
         <v>277536800</v>
       </c>
       <c r="C132" t="n">
-        <v>689336.9365930443</v>
+        <v>2949278.555873415</v>
       </c>
     </row>
     <row r="133">
@@ -45462,7 +46527,7 @@
         <v>277536800</v>
       </c>
       <c r="C133" t="n">
-        <v>692214.6865930443</v>
+        <v>2952156.305873415</v>
       </c>
     </row>
     <row r="134">
@@ -45473,7 +46538,7 @@
         <v>277536800</v>
       </c>
       <c r="C134" t="n">
-        <v>692214.6865930443</v>
+        <v>2952156.305873415</v>
       </c>
     </row>
     <row r="135">
@@ -45484,7 +46549,7 @@
         <v>277536800</v>
       </c>
       <c r="C135" t="n">
-        <v>695092.4365930443</v>
+        <v>2955034.055873415</v>
       </c>
     </row>
     <row r="136">
@@ -45495,7 +46560,7 @@
         <v>277536800</v>
       </c>
       <c r="C136" t="n">
-        <v>697970.1865930443</v>
+        <v>2957911.805873415</v>
       </c>
     </row>
     <row r="137">
@@ -45506,7 +46571,7 @@
         <v>277536800</v>
       </c>
       <c r="C137" t="n">
-        <v>700847.9365930443</v>
+        <v>2960789.555873415</v>
       </c>
     </row>
     <row r="138">
@@ -45517,7 +46582,7 @@
         <v>277536800</v>
       </c>
       <c r="C138" t="n">
-        <v>700024.448650833</v>
+        <v>2959966.067931204</v>
       </c>
     </row>
     <row r="139">
@@ -45528,7 +46593,7 @@
         <v>277536800</v>
       </c>
       <c r="C139" t="n">
-        <v>692419.548650833</v>
+        <v>2952361.167931204</v>
       </c>
     </row>
     <row r="140">
@@ -45539,7 +46604,7 @@
         <v>277536800</v>
       </c>
       <c r="C140" t="n">
-        <v>684814.6486508329</v>
+        <v>2944756.267931204</v>
       </c>
     </row>
     <row r="141">
@@ -45550,7 +46615,7 @@
         <v>277536800</v>
       </c>
       <c r="C141" t="n">
-        <v>677209.7486508329</v>
+        <v>2937151.367931204</v>
       </c>
     </row>
     <row r="142">
@@ -45561,7 +46626,7 @@
         <v>277536800</v>
       </c>
       <c r="C142" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="143">
@@ -45572,7 +46637,7 @@
         <v>277536800</v>
       </c>
       <c r="C143" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="144">
@@ -45583,7 +46648,7 @@
         <v>277536800</v>
       </c>
       <c r="C144" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="145">
@@ -45594,7 +46659,7 @@
         <v>277536800</v>
       </c>
       <c r="C145" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="146">
@@ -45605,7 +46670,7 @@
         <v>277536800</v>
       </c>
       <c r="C146" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="147">
@@ -45616,7 +46681,7 @@
         <v>277536800</v>
       </c>
       <c r="C147" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="148">
@@ -45627,7 +46692,7 @@
         <v>277536800</v>
       </c>
       <c r="C148" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="149">
@@ -45638,7 +46703,7 @@
         <v>277536800</v>
       </c>
       <c r="C149" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="150">
@@ -45649,7 +46714,7 @@
         <v>277536800</v>
       </c>
       <c r="C150" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="151">
@@ -45660,7 +46725,7 @@
         <v>277536800</v>
       </c>
       <c r="C151" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="152">
@@ -45671,7 +46736,7 @@
         <v>277536800</v>
       </c>
       <c r="C152" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="153">
@@ -45682,7 +46747,7 @@
         <v>277536800</v>
       </c>
       <c r="C153" t="n">
-        <v>676382.4124509819</v>
+        <v>2936324.031731354</v>
       </c>
     </row>
     <row r="154">
@@ -45693,7 +46758,7 @@
         <v>277536800</v>
       </c>
       <c r="C154" t="n">
-        <v>677765.4795965857</v>
+        <v>2937707.098876957</v>
       </c>
     </row>
     <row r="155">
@@ -45704,7 +46769,7 @@
         <v>277536800</v>
       </c>
       <c r="C155" t="n">
-        <v>680643.2295965857</v>
+        <v>2940584.848876957</v>
       </c>
     </row>
     <row r="156">
@@ -45715,7 +46780,7 @@
         <v>277536800</v>
       </c>
       <c r="C156" t="n">
-        <v>683520.9795965857</v>
+        <v>2943462.598876957</v>
       </c>
     </row>
     <row r="157">
@@ -45726,7 +46791,7 @@
         <v>277536800</v>
       </c>
       <c r="C157" t="n">
-        <v>686398.7295965857</v>
+        <v>2946340.348876957</v>
       </c>
     </row>
     <row r="158">
@@ -45737,7 +46802,7 @@
         <v>277536800</v>
       </c>
       <c r="C158" t="n">
-        <v>689276.4795965857</v>
+        <v>2949218.098876957</v>
       </c>
     </row>
     <row r="159">
@@ -45748,7 +46813,7 @@
         <v>277536800</v>
       </c>
       <c r="C159" t="n">
-        <v>689276.4795965857</v>
+        <v>2949218.098876957</v>
       </c>
     </row>
     <row r="160">
@@ -45759,7 +46824,7 @@
         <v>277536800</v>
       </c>
       <c r="C160" t="n">
-        <v>692154.2295965857</v>
+        <v>2952095.848876957</v>
       </c>
     </row>
     <row r="161">
@@ -45770,7 +46835,7 @@
         <v>277536800</v>
       </c>
       <c r="C161" t="n">
-        <v>695031.9795965857</v>
+        <v>2954973.598876957</v>
       </c>
     </row>
     <row r="162">
@@ -45778,10 +46843,10 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C162" t="n">
-        <v>695031.9795965857</v>
+        <v>2954973.598876957</v>
       </c>
     </row>
     <row r="163">
@@ -45789,10 +46854,10 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C163" t="n">
-        <v>688506.5634177778</v>
+        <v>2948448.182698149</v>
       </c>
     </row>
     <row r="164">
@@ -45800,10 +46865,10 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C164" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="165">
@@ -45811,10 +46876,10 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C165" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="166">
@@ -45822,10 +46887,10 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C166" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="167">
@@ -45833,10 +46898,10 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C167" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="168">
@@ -45844,10 +46909,10 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C168" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
     <row r="169">
@@ -45855,10 +46920,10 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>277536800</v>
+        <v>277538823.0693793</v>
       </c>
       <c r="C169" t="n">
-        <v>686952.752459793</v>
+        <v>2946894.371740164</v>
       </c>
     </row>
   </sheetData>
@@ -48881,7 +49946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49929,6 +50994,55 @@
       </c>
       <c r="M21" t="n">
         <v>9000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MA_ES_interconexion_hidrogeno</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MA_hydrogen_bus</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ES_hydrogen_bus</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3742.94</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3742.94</v>
       </c>
     </row>
   </sheetData>
@@ -50798,7 +51912,7 @@
         <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>3837</v>
+        <v>842.6120012762646</v>
       </c>
       <c r="J17" t="n">
         <v>2450.59619</v>
@@ -51630,7 +52744,7 @@
         <v>-0</v>
       </c>
       <c r="C34" t="n">
-        <v>2697.425839106242</v>
+        <v>13320.7506329652</v>
       </c>
       <c r="D34" t="n">
         <v>1290.58597984176</v>
@@ -53680,7 +54794,7 @@
         <v>-0</v>
       </c>
       <c r="C75" t="n">
-        <v>13320.7506329652</v>
+        <v>-0</v>
       </c>
       <c r="D75" t="n">
         <v>7347.237160691578</v>
@@ -53748,7 +54862,7 @@
         <v>-0</v>
       </c>
       <c r="I76" t="n">
-        <v>-0</v>
+        <v>1634.351088428555</v>
       </c>
       <c r="J76" t="n">
         <v>1683.759498571429</v>
@@ -53898,7 +55012,7 @@
         <v>-0</v>
       </c>
       <c r="I79" t="n">
-        <v>-0</v>
+        <v>1928.143704335475</v>
       </c>
       <c r="J79" t="n">
         <v>1823.697322857143</v>
@@ -54248,7 +55362,7 @@
         <v>-0</v>
       </c>
       <c r="I86" t="n">
-        <v>568.1067940425128</v>
+        <v>-0</v>
       </c>
       <c r="J86" t="n">
         <v>2236.145644285714</v>
@@ -54445,7 +55559,7 @@
         <v>-0</v>
       </c>
       <c r="H90" t="n">
-        <v>5335.108485979174</v>
+        <v>3678.418319851702</v>
       </c>
       <c r="I90" t="n">
         <v>-0</v>
@@ -54645,7 +55759,7 @@
         <v>-0</v>
       </c>
       <c r="H94" t="n">
-        <v>5009.729374738103</v>
+        <v>6666.419540865573</v>
       </c>
       <c r="I94" t="n">
         <v>-0</v>
@@ -58030,7 +59144,7 @@
         <v>-0</v>
       </c>
       <c r="C162" t="n">
-        <v>-0</v>
+        <v>2697.425839106242</v>
       </c>
       <c r="D162" t="n">
         <v>15500</v>
@@ -59289,7 +60403,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-2877.75</v>
+        <v>-631.9590009571984</v>
       </c>
       <c r="J17" t="n">
         <v>-1715.417333</v>
@@ -60121,7 +61235,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-2023.069379329681</v>
+        <v>-9990.5629747239</v>
       </c>
       <c r="D34" t="n">
         <v>-903.4101858892318</v>
@@ -62171,7 +63285,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>-9990.5629747239</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>-5143.066012484104</v>
@@ -62239,7 +63353,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>-1225.763316321416</v>
       </c>
       <c r="J76" t="n">
         <v>-1178.631649</v>
@@ -62389,7 +63503,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>-1446.107778251606</v>
       </c>
       <c r="J79" t="n">
         <v>-1276.588126</v>
@@ -62739,7 +63853,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>-426.0800955318846</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>-1565.301951</v>
@@ -62936,7 +64050,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-4534.842213082297</v>
+        <v>-3126.655571873946</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -63136,7 +64250,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-4258.269968527387</v>
+        <v>-5666.456609735737</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -66521,7 +67635,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>-2023.069379329681</v>
       </c>
       <c r="D162" t="n">
         <v>-10850</v>
